--- a/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
   <si>
     <t>Record</t>
   </si>
@@ -36,115 +36,115 @@
     <t>Fumbledore</t>
   </si>
   <si>
+    <t>CeeDeez TDs</t>
+  </si>
+  <si>
     <t>GibbsMe All Your Lovin'</t>
   </si>
   <si>
-    <t>CeeDeez TDs</t>
+    <t>Chasing the W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shannon Fannin Bijannin </t>
   </si>
   <si>
     <t>asholes</t>
   </si>
   <si>
-    <t>Chasing the W</t>
-  </si>
-  <si>
     <t>LUKEWARMRANCH</t>
   </si>
   <si>
     <t>Dietz NUTZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Shannon Fannin Bijannin </t>
-  </si>
-  <si>
     <t xml:space="preserve">Maye Baddd </t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>95.0%</t>
-  </si>
-  <si>
-    <t>94.7%</t>
-  </si>
-  <si>
-    <t>90.4%</t>
-  </si>
-  <si>
-    <t>49.4%</t>
-  </si>
-  <si>
-    <t>33.4%</t>
-  </si>
-  <si>
-    <t>26.5%</t>
-  </si>
-  <si>
-    <t>6.0%</t>
-  </si>
-  <si>
-    <t>4.8%</t>
+    <t>99.4%</t>
+  </si>
+  <si>
+    <t>96.0%</t>
+  </si>
+  <si>
+    <t>87.6%</t>
+  </si>
+  <si>
+    <t>84.3%</t>
+  </si>
+  <si>
+    <t>44.4%</t>
+  </si>
+  <si>
+    <t>34.4%</t>
+  </si>
+  <si>
+    <t>30.2%</t>
+  </si>
+  <si>
+    <t>22.1%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-1900</t>
-  </si>
-  <si>
-    <t>-1787</t>
-  </si>
-  <si>
-    <t>-942</t>
-  </si>
-  <si>
-    <t>+102</t>
-  </si>
-  <si>
-    <t>+199</t>
-  </si>
-  <si>
-    <t>+277</t>
-  </si>
-  <si>
-    <t>+1567</t>
-  </si>
-  <si>
-    <t>+1983</t>
+    <t>-16567</t>
+  </si>
+  <si>
+    <t>-2400</t>
+  </si>
+  <si>
+    <t>-706</t>
+  </si>
+  <si>
+    <t>-537</t>
+  </si>
+  <si>
+    <t>+125</t>
+  </si>
+  <si>
+    <t>+191</t>
+  </si>
+  <si>
+    <t>+231</t>
+  </si>
+  <si>
+    <t>+352</t>
+  </si>
+  <si>
+    <t>+6150</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>51.4%</t>
-  </si>
-  <si>
-    <t>39.4%</t>
-  </si>
-  <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
+    <t>61.1%</t>
+  </si>
+  <si>
+    <t>32.6%</t>
+  </si>
+  <si>
+    <t>4.1%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -156,19 +156,16 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-106</t>
-  </si>
-  <si>
-    <t>+154</t>
-  </si>
-  <si>
-    <t>+2841</t>
-  </si>
-  <si>
-    <t>+3025</t>
-  </si>
-  <si>
-    <t>+4248</t>
+    <t>-157</t>
+  </si>
+  <si>
+    <t>+207</t>
+  </si>
+  <si>
+    <t>+2339</t>
+  </si>
+  <si>
+    <t>+5782</t>
   </si>
   <si>
     <t>+49900</t>
@@ -177,28 +174,40 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>46.5%</t>
-  </si>
-  <si>
-    <t>34.8%</t>
-  </si>
-  <si>
-    <t>9.5%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
-  </si>
-  <si>
-    <t>+115</t>
-  </si>
-  <si>
-    <t>+187</t>
-  </si>
-  <si>
-    <t>+953</t>
-  </si>
-  <si>
-    <t>+3233</t>
+    <t>68.9%</t>
+  </si>
+  <si>
+    <t>11.9%</t>
+  </si>
+  <si>
+    <t>8.3%</t>
+  </si>
+  <si>
+    <t>5.7%</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
+  </si>
+  <si>
+    <t>-222</t>
+  </si>
+  <si>
+    <t>+740</t>
+  </si>
+  <si>
+    <t>+1105</t>
+  </si>
+  <si>
+    <t>+1654</t>
+  </si>
+  <si>
+    <t>+2173</t>
+  </si>
+  <si>
+    <t>+12400</t>
   </si>
 </sst>
 </file>
@@ -581,10 +590,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -595,10 +604,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -606,13 +615,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -623,10 +632,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -637,10 +646,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -648,13 +657,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -662,13 +671,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -676,13 +685,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -693,10 +702,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -704,13 +713,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -731,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -745,7 +754,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>46</v>
@@ -759,7 +768,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>47</v>
@@ -770,10 +779,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
@@ -787,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>49</v>
@@ -801,7 +810,7 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>50</v>
@@ -809,35 +818,35 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -846,26 +855,26 @@
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
@@ -874,7 +883,7 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -906,13 +915,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -923,10 +932,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -934,13 +943,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -948,13 +957,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -962,46 +971,46 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -1010,7 +1019,7 @@
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1024,7 +1033,7 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1038,7 +1047,7 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
@@ -33,121 +33,118 @@
     <t>Amanda's Awesome Team</t>
   </si>
   <si>
+    <t>CeeDeez TDs</t>
+  </si>
+  <si>
     <t>Fumbledore</t>
   </si>
   <si>
-    <t>CeeDeez TDs</t>
+    <t>LUKEWARMRANCH</t>
+  </si>
+  <si>
+    <t>Chasing the W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shannon Fannin Bijannin </t>
   </si>
   <si>
     <t>GibbsMe All Your Lovin'</t>
   </si>
   <si>
-    <t>Chasing the W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shannon Fannin Bijannin </t>
+    <t>Dietz NUTZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maye Baddd </t>
   </si>
   <si>
     <t>asholes</t>
   </si>
   <si>
-    <t>LUKEWARMRANCH</t>
-  </si>
-  <si>
-    <t>Dietz NUTZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maye Baddd </t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
+    <t>99.6%</t>
+  </si>
+  <si>
     <t>99.4%</t>
   </si>
   <si>
-    <t>96.0%</t>
-  </si>
-  <si>
-    <t>87.6%</t>
-  </si>
-  <si>
-    <t>84.3%</t>
-  </si>
-  <si>
-    <t>44.4%</t>
-  </si>
-  <si>
-    <t>34.4%</t>
-  </si>
-  <si>
-    <t>30.2%</t>
-  </si>
-  <si>
-    <t>22.1%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
+    <t>72.6%</t>
+  </si>
+  <si>
+    <t>64.2%</t>
+  </si>
+  <si>
+    <t>56.3%</t>
+  </si>
+  <si>
+    <t>39.5%</t>
+  </si>
+  <si>
+    <t>38.3%</t>
+  </si>
+  <si>
+    <t>18.1%</t>
+  </si>
+  <si>
+    <t>12.0%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
+    <t>-24900</t>
+  </si>
+  <si>
     <t>-16567</t>
   </si>
   <si>
-    <t>-2400</t>
-  </si>
-  <si>
-    <t>-706</t>
-  </si>
-  <si>
-    <t>-537</t>
-  </si>
-  <si>
-    <t>+125</t>
-  </si>
-  <si>
-    <t>+191</t>
-  </si>
-  <si>
-    <t>+231</t>
-  </si>
-  <si>
-    <t>+352</t>
-  </si>
-  <si>
-    <t>+6150</t>
+    <t>-265</t>
+  </si>
+  <si>
+    <t>-179</t>
+  </si>
+  <si>
+    <t>-129</t>
+  </si>
+  <si>
+    <t>+153</t>
+  </si>
+  <si>
+    <t>+161</t>
+  </si>
+  <si>
+    <t>+452</t>
+  </si>
+  <si>
+    <t>+733</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>61.1%</t>
-  </si>
-  <si>
-    <t>32.6%</t>
-  </si>
-  <si>
-    <t>4.1%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>67.0%</t>
+  </si>
+  <si>
+    <t>22.0%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -156,58 +153,61 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-157</t>
-  </si>
-  <si>
-    <t>+207</t>
-  </si>
-  <si>
-    <t>+2339</t>
-  </si>
-  <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>-203</t>
+  </si>
+  <si>
+    <t>+355</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+14186</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>68.9%</t>
-  </si>
-  <si>
-    <t>11.9%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
-  </si>
-  <si>
-    <t>5.7%</t>
-  </si>
-  <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>-222</t>
-  </si>
-  <si>
-    <t>+740</t>
-  </si>
-  <si>
-    <t>+1105</t>
-  </si>
-  <si>
-    <t>+1654</t>
-  </si>
-  <si>
-    <t>+2173</t>
-  </si>
-  <si>
-    <t>+12400</t>
+    <t>36.6%</t>
+  </si>
+  <si>
+    <t>28.2%</t>
+  </si>
+  <si>
+    <t>13.8%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>+173</t>
+  </si>
+  <si>
+    <t>+255</t>
+  </si>
+  <si>
+    <t>+625</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+1393</t>
+  </si>
+  <si>
+    <t>+3746</t>
+  </si>
+  <si>
+    <t>+4067</t>
   </si>
 </sst>
 </file>
@@ -629,7 +629,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -643,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -657,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -685,7 +685,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -699,7 +699,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -757,12 +757,12 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -771,12 +771,12 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -785,7 +785,7 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -793,13 +793,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -807,83 +807,83 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -918,10 +918,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -929,13 +929,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -943,13 +943,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -960,10 +960,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -971,13 +971,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -985,27 +985,27 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1016,24 +1016,24 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1044,10 +1044,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
   <si>
     <t>Record</t>
   </si>
@@ -30,184 +30,208 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Fumbledore</t>
+  </si>
+  <si>
     <t>Amanda's Awesome Team</t>
   </si>
   <si>
+    <t>LUKEWARMRANCH</t>
+  </si>
+  <si>
+    <t>GibbsMe All Your Lovin'</t>
+  </si>
+  <si>
     <t>CeeDeez TDs</t>
   </si>
   <si>
-    <t>Fumbledore</t>
-  </si>
-  <si>
-    <t>LUKEWARMRANCH</t>
-  </si>
-  <si>
     <t>Chasing the W</t>
   </si>
   <si>
+    <t xml:space="preserve">Maye Baddd </t>
+  </si>
+  <si>
     <t xml:space="preserve">Shannon Fannin Bijannin </t>
   </si>
   <si>
-    <t>GibbsMe All Your Lovin'</t>
-  </si>
-  <si>
     <t>Dietz NUTZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Maye Baddd </t>
-  </si>
-  <si>
     <t>asholes</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>99.6%</t>
-  </si>
-  <si>
-    <t>99.4%</t>
-  </si>
-  <si>
-    <t>72.6%</t>
-  </si>
-  <si>
-    <t>64.2%</t>
-  </si>
-  <si>
-    <t>56.3%</t>
-  </si>
-  <si>
-    <t>39.5%</t>
-  </si>
-  <si>
-    <t>38.3%</t>
-  </si>
-  <si>
-    <t>18.1%</t>
-  </si>
-  <si>
-    <t>12.0%</t>
-  </si>
-  <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-24900</t>
-  </si>
-  <si>
-    <t>-16567</t>
-  </si>
-  <si>
-    <t>-265</t>
-  </si>
-  <si>
-    <t>-179</t>
-  </si>
-  <si>
-    <t>-129</t>
-  </si>
-  <si>
-    <t>+153</t>
-  </si>
-  <si>
-    <t>+161</t>
-  </si>
-  <si>
-    <t>+452</t>
-  </si>
-  <si>
-    <t>+733</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>98.3%</t>
+  </si>
+  <si>
+    <t>97.3%</t>
+  </si>
+  <si>
+    <t>94.1%</t>
+  </si>
+  <si>
+    <t>75.4%</t>
+  </si>
+  <si>
+    <t>75.0%</t>
+  </si>
+  <si>
+    <t>65.2%</t>
+  </si>
+  <si>
+    <t>42.8%</t>
+  </si>
+  <si>
+    <t>23.5%</t>
+  </si>
+  <si>
+    <t>17.2%</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>-5782</t>
+  </si>
+  <si>
+    <t>-3604</t>
+  </si>
+  <si>
+    <t>-1595</t>
+  </si>
+  <si>
+    <t>-307</t>
+  </si>
+  <si>
+    <t>-300</t>
+  </si>
+  <si>
+    <t>-187</t>
+  </si>
+  <si>
+    <t>+134</t>
+  </si>
+  <si>
+    <t>+326</t>
+  </si>
+  <si>
+    <t>+481</t>
+  </si>
+  <si>
+    <t>+793</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>67.0%</t>
-  </si>
-  <si>
-    <t>22.0%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
+    <t>49.9%</t>
+  </si>
+  <si>
+    <t>26.7%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
+    <t>+100</t>
+  </si>
+  <si>
+    <t>+275</t>
+  </si>
+  <si>
+    <t>+533</t>
+  </si>
+  <si>
+    <t>+3471</t>
+  </si>
+  <si>
+    <t>+3746</t>
+  </si>
+  <si>
+    <t>+6567</t>
+  </si>
+  <si>
+    <t>+24900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>36.2%</t>
+  </si>
+  <si>
+    <t>27.7%</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>2.2%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-203</t>
-  </si>
-  <si>
-    <t>+355</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>36.6%</t>
-  </si>
-  <si>
-    <t>28.2%</t>
-  </si>
-  <si>
-    <t>13.8%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>6.7%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
-    <t>+173</t>
-  </si>
-  <si>
-    <t>+255</t>
-  </si>
-  <si>
-    <t>+625</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+1393</t>
-  </si>
-  <si>
-    <t>+3746</t>
-  </si>
-  <si>
-    <t>+4067</t>
+    <t>+176</t>
+  </si>
+  <si>
+    <t>+261</t>
+  </si>
+  <si>
+    <t>+395</t>
+  </si>
+  <si>
+    <t>+1090</t>
+  </si>
+  <si>
+    <t>+3025</t>
+  </si>
+  <si>
+    <t>+4445</t>
+  </si>
+  <si>
+    <t>+5456</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -601,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -629,7 +653,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -643,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -657,7 +681,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -713,7 +737,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -757,26 +781,26 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -785,7 +809,7 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -793,13 +817,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -807,13 +831,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -821,55 +845,55 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -877,13 +901,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -915,13 +939,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -932,10 +956,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -946,10 +970,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -960,10 +984,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -971,13 +995,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -985,13 +1009,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -999,13 +1023,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1016,38 +1040,38 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
   <si>
     <t>Record</t>
   </si>
@@ -39,199 +39,211 @@
     <t>LUKEWARMRANCH</t>
   </si>
   <si>
+    <t>CeeDeez TDs</t>
+  </si>
+  <si>
+    <t>Chasing the W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maye Baddd </t>
+  </si>
+  <si>
     <t>GibbsMe All Your Lovin'</t>
   </si>
   <si>
-    <t>CeeDeez TDs</t>
-  </si>
-  <si>
-    <t>Chasing the W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maye Baddd </t>
-  </si>
-  <si>
     <t xml:space="preserve">Shannon Fannin Bijannin </t>
   </si>
   <si>
+    <t>asholes</t>
+  </si>
+  <si>
     <t>Dietz NUTZ</t>
   </si>
   <si>
-    <t>asholes</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>98.3%</t>
-  </si>
-  <si>
-    <t>97.3%</t>
-  </si>
-  <si>
-    <t>94.1%</t>
-  </si>
-  <si>
-    <t>75.4%</t>
-  </si>
-  <si>
-    <t>75.0%</t>
-  </si>
-  <si>
-    <t>65.2%</t>
-  </si>
-  <si>
-    <t>42.8%</t>
-  </si>
-  <si>
-    <t>23.5%</t>
-  </si>
-  <si>
-    <t>17.2%</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>-5782</t>
-  </si>
-  <si>
-    <t>-3604</t>
-  </si>
-  <si>
-    <t>-1595</t>
-  </si>
-  <si>
-    <t>-307</t>
-  </si>
-  <si>
-    <t>-300</t>
-  </si>
-  <si>
-    <t>-187</t>
-  </si>
-  <si>
-    <t>+134</t>
-  </si>
-  <si>
-    <t>+326</t>
-  </si>
-  <si>
-    <t>+481</t>
-  </si>
-  <si>
-    <t>+793</t>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>96.2%</t>
+  </si>
+  <si>
+    <t>92.1%</t>
+  </si>
+  <si>
+    <t>87.1%</t>
+  </si>
+  <si>
+    <t>85.5%</t>
+  </si>
+  <si>
+    <t>80.3%</t>
+  </si>
+  <si>
+    <t>57.6%</t>
+  </si>
+  <si>
+    <t>38.8%</t>
+  </si>
+  <si>
+    <t>34.3%</t>
+  </si>
+  <si>
+    <t>19.9%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>-2532</t>
+  </si>
+  <si>
+    <t>-1166</t>
+  </si>
+  <si>
+    <t>-675</t>
+  </si>
+  <si>
+    <t>-590</t>
+  </si>
+  <si>
+    <t>-408</t>
+  </si>
+  <si>
+    <t>-136</t>
+  </si>
+  <si>
+    <t>+158</t>
+  </si>
+  <si>
+    <t>+192</t>
+  </si>
+  <si>
+    <t>+403</t>
+  </si>
+  <si>
+    <t>+1120</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>49.9%</t>
-  </si>
-  <si>
-    <t>26.7%</t>
-  </si>
-  <si>
-    <t>15.8%</t>
+    <t>38.3%</t>
+  </si>
+  <si>
+    <t>19.8%</t>
+  </si>
+  <si>
+    <t>15.6%</t>
+  </si>
+  <si>
+    <t>12.6%</t>
+  </si>
+  <si>
+    <t>9.3%</t>
   </si>
   <si>
     <t>2.8%</t>
   </si>
   <si>
-    <t>2.6%</t>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>+161</t>
+  </si>
+  <si>
+    <t>+405</t>
+  </si>
+  <si>
+    <t>+541</t>
+  </si>
+  <si>
+    <t>+694</t>
+  </si>
+  <si>
+    <t>+975</t>
+  </si>
+  <si>
+    <t>+3471</t>
+  </si>
+  <si>
+    <t>+11011</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>50.1%</t>
+  </si>
+  <si>
+    <t>23.0%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
   </si>
   <si>
     <t>1.5%</t>
   </si>
   <si>
+    <t>1.2%</t>
+  </si>
+  <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>+100</t>
-  </si>
-  <si>
-    <t>+275</t>
-  </si>
-  <si>
-    <t>+533</t>
-  </si>
-  <si>
-    <t>+3471</t>
-  </si>
-  <si>
-    <t>+3746</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-100</t>
+  </si>
+  <si>
+    <t>+335</t>
+  </si>
+  <si>
+    <t>+862</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+2757</t>
   </si>
   <si>
     <t>+6567</t>
   </si>
   <si>
+    <t>+8233</t>
+  </si>
+  <si>
     <t>+24900</t>
   </si>
   <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>36.2%</t>
-  </si>
-  <si>
-    <t>27.7%</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+176</t>
-  </si>
-  <si>
-    <t>+261</t>
-  </si>
-  <si>
-    <t>+395</t>
-  </si>
-  <si>
-    <t>+1090</t>
-  </si>
-  <si>
-    <t>+3025</t>
-  </si>
-  <si>
-    <t>+4445</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -653,7 +665,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -681,7 +693,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -695,7 +707,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -709,7 +721,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -723,7 +735,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -737,7 +749,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -781,7 +793,7 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -795,7 +807,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -809,7 +821,7 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -817,13 +829,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -837,7 +849,7 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -845,13 +857,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -859,41 +871,41 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -901,13 +913,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -939,13 +951,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -953,13 +965,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -967,13 +979,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -981,13 +993,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -995,13 +1007,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1012,38 +1024,38 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1054,10 +1066,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1068,10 +1080,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t>Record</t>
   </si>
@@ -33,217 +33,193 @@
     <t>Fumbledore</t>
   </si>
   <si>
+    <t>CeeDeez TDs</t>
+  </si>
+  <si>
+    <t>LUKEWARMRANCH</t>
+  </si>
+  <si>
     <t>Amanda's Awesome Team</t>
   </si>
   <si>
-    <t>LUKEWARMRANCH</t>
-  </si>
-  <si>
-    <t>CeeDeez TDs</t>
-  </si>
-  <si>
     <t>Chasing the W</t>
   </si>
   <si>
     <t xml:space="preserve">Maye Baddd </t>
   </si>
   <si>
+    <t>asholes</t>
+  </si>
+  <si>
     <t>GibbsMe All Your Lovin'</t>
   </si>
   <si>
+    <t>Dietz NUTZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shannon Fannin Bijannin </t>
   </si>
   <si>
-    <t>asholes</t>
-  </si>
-  <si>
-    <t>Dietz NUTZ</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>96.2%</t>
-  </si>
-  <si>
-    <t>92.1%</t>
-  </si>
-  <si>
-    <t>87.1%</t>
-  </si>
-  <si>
-    <t>85.5%</t>
-  </si>
-  <si>
-    <t>80.3%</t>
-  </si>
-  <si>
-    <t>57.6%</t>
-  </si>
-  <si>
-    <t>38.8%</t>
-  </si>
-  <si>
-    <t>34.3%</t>
-  </si>
-  <si>
-    <t>19.9%</t>
-  </si>
-  <si>
-    <t>8.2%</t>
-  </si>
-  <si>
-    <t>-2532</t>
-  </si>
-  <si>
-    <t>-1166</t>
-  </si>
-  <si>
-    <t>-675</t>
-  </si>
-  <si>
-    <t>-590</t>
-  </si>
-  <si>
-    <t>-408</t>
-  </si>
-  <si>
-    <t>-136</t>
-  </si>
-  <si>
-    <t>+158</t>
-  </si>
-  <si>
-    <t>+192</t>
-  </si>
-  <si>
-    <t>+403</t>
-  </si>
-  <si>
-    <t>+1120</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>99.4%</t>
+  </si>
+  <si>
+    <t>97.8%</t>
+  </si>
+  <si>
+    <t>95.9%</t>
+  </si>
+  <si>
+    <t>75.6%</t>
+  </si>
+  <si>
+    <t>60.8%</t>
+  </si>
+  <si>
+    <t>52.0%</t>
+  </si>
+  <si>
+    <t>41.6%</t>
+  </si>
+  <si>
+    <t>35.5%</t>
+  </si>
+  <si>
+    <t>23.8%</t>
+  </si>
+  <si>
+    <t>17.6%</t>
+  </si>
+  <si>
+    <t>-16567</t>
+  </si>
+  <si>
+    <t>-4445</t>
+  </si>
+  <si>
+    <t>-2339</t>
+  </si>
+  <si>
+    <t>-310</t>
+  </si>
+  <si>
+    <t>-155</t>
+  </si>
+  <si>
+    <t>-108</t>
+  </si>
+  <si>
+    <t>+140</t>
+  </si>
+  <si>
+    <t>+182</t>
+  </si>
+  <si>
+    <t>+320</t>
+  </si>
+  <si>
+    <t>+468</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>38.3%</t>
-  </si>
-  <si>
-    <t>19.8%</t>
-  </si>
-  <si>
-    <t>15.6%</t>
-  </si>
-  <si>
-    <t>12.6%</t>
-  </si>
-  <si>
-    <t>9.3%</t>
-  </si>
-  <si>
-    <t>2.8%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
+    <t>47.0%</t>
+  </si>
+  <si>
+    <t>25.9%</t>
+  </si>
+  <si>
+    <t>21.9%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>+113</t>
+  </si>
+  <si>
+    <t>+286</t>
+  </si>
+  <si>
+    <t>+357</t>
+  </si>
+  <si>
+    <t>+4248</t>
+  </si>
+  <si>
+    <t>+8233</t>
+  </si>
+  <si>
+    <t>+14186</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>33.2%</t>
+  </si>
+  <si>
+    <t>23.6%</t>
+  </si>
+  <si>
+    <t>17.0%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>5.9%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+161</t>
-  </si>
-  <si>
-    <t>+405</t>
-  </si>
-  <si>
-    <t>+541</t>
-  </si>
-  <si>
-    <t>+694</t>
-  </si>
-  <si>
-    <t>+975</t>
-  </si>
-  <si>
-    <t>+3471</t>
-  </si>
-  <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>50.1%</t>
-  </si>
-  <si>
-    <t>23.0%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>-100</t>
-  </si>
-  <si>
-    <t>+335</t>
-  </si>
-  <si>
-    <t>+862</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+2757</t>
-  </si>
-  <si>
-    <t>+6567</t>
-  </si>
-  <si>
-    <t>+8233</t>
-  </si>
-  <si>
-    <t>+24900</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>+201</t>
+  </si>
+  <si>
+    <t>+324</t>
+  </si>
+  <si>
+    <t>+488</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1595</t>
+  </si>
+  <si>
+    <t>+4900</t>
   </si>
 </sst>
 </file>
@@ -665,7 +641,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -679,7 +655,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -693,7 +669,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -735,7 +711,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -793,7 +769,7 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -807,7 +783,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -821,7 +797,7 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -829,13 +805,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -843,13 +819,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -857,13 +833,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -874,10 +850,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -888,10 +864,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -899,13 +875,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -916,10 +892,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -954,10 +930,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -965,13 +941,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -982,38 +958,38 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1021,41 +997,41 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1066,10 +1042,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1080,10 +1056,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
+++ b/data/odds/Fantasy 2026 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="73">
   <si>
     <t>Record</t>
   </si>
@@ -72,25 +72,121 @@
     <t>2-5</t>
   </si>
   <si>
-    <t>99.4%</t>
-  </si>
-  <si>
-    <t>97.8%</t>
+    <t>99.5%</t>
+  </si>
+  <si>
+    <t>98.2%</t>
   </si>
   <si>
     <t>95.9%</t>
   </si>
   <si>
-    <t>75.6%</t>
-  </si>
-  <si>
-    <t>60.8%</t>
-  </si>
-  <si>
-    <t>52.0%</t>
-  </si>
-  <si>
-    <t>41.6%</t>
+    <t>72.8%</t>
+  </si>
+  <si>
+    <t>63.9%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>42.2%</t>
+  </si>
+  <si>
+    <t>37.2%</t>
+  </si>
+  <si>
+    <t>22.9%</t>
+  </si>
+  <si>
+    <t>17.4%</t>
+  </si>
+  <si>
+    <t>-19900</t>
+  </si>
+  <si>
+    <t>-5456</t>
+  </si>
+  <si>
+    <t>-2339</t>
+  </si>
+  <si>
+    <t>-268</t>
+  </si>
+  <si>
+    <t>-177</t>
+  </si>
+  <si>
+    <t>-100</t>
+  </si>
+  <si>
+    <t>+137</t>
+  </si>
+  <si>
+    <t>+169</t>
+  </si>
+  <si>
+    <t>+337</t>
+  </si>
+  <si>
+    <t>+475</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>47.3%</t>
+  </si>
+  <si>
+    <t>24.8%</t>
+  </si>
+  <si>
+    <t>21.2%</t>
+  </si>
+  <si>
+    <t>3.1%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>+111</t>
+  </si>
+  <si>
+    <t>+303</t>
+  </si>
+  <si>
+    <t>+372</t>
+  </si>
+  <si>
+    <t>+3126</t>
+  </si>
+  <si>
+    <t>+8233</t>
+  </si>
+  <si>
+    <t>+12400</t>
+  </si>
+  <si>
+    <t>+14186</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
   <si>
     <t>35.5%</t>
@@ -99,28 +195,22 @@
     <t>23.8%</t>
   </si>
   <si>
-    <t>17.6%</t>
-  </si>
-  <si>
-    <t>-16567</t>
-  </si>
-  <si>
-    <t>-4445</t>
-  </si>
-  <si>
-    <t>-2339</t>
-  </si>
-  <si>
-    <t>-310</t>
-  </si>
-  <si>
-    <t>-155</t>
-  </si>
-  <si>
-    <t>-108</t>
-  </si>
-  <si>
-    <t>+140</t>
+    <t>16.2%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>8.1%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
   </si>
   <si>
     <t>+182</t>
@@ -129,97 +219,22 @@
     <t>+320</t>
   </si>
   <si>
-    <t>+468</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>47.0%</t>
-  </si>
-  <si>
-    <t>25.9%</t>
-  </si>
-  <si>
-    <t>21.9%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+113</t>
-  </si>
-  <si>
-    <t>+286</t>
-  </si>
-  <si>
-    <t>+357</t>
-  </si>
-  <si>
-    <t>+4248</t>
-  </si>
-  <si>
-    <t>+8233</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>+517</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+1135</t>
+  </si>
+  <si>
+    <t>+2930</t>
+  </si>
+  <si>
+    <t>+3025</t>
   </si>
   <si>
     <t>+99900</t>
-  </si>
-  <si>
-    <t>33.2%</t>
-  </si>
-  <si>
-    <t>23.6%</t>
-  </si>
-  <si>
-    <t>17.0%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>+201</t>
-  </si>
-  <si>
-    <t>+324</t>
-  </si>
-  <si>
-    <t>+488</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+1595</t>
-  </si>
-  <si>
-    <t>+4900</t>
   </si>
 </sst>
 </file>
@@ -769,7 +784,7 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -783,7 +798,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -797,7 +812,7 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -811,7 +826,7 @@
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -825,7 +840,7 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -839,7 +854,7 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -850,10 +865,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -864,10 +879,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -878,10 +893,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -892,10 +907,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -930,10 +945,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -944,10 +959,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -958,38 +973,38 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1000,10 +1015,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1014,10 +1029,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1028,10 +1043,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1042,10 +1057,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1056,10 +1071,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
